--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:25</t>
+    <t xml:space="preserve">2026-09-10 01:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:40</t>
+    <t xml:space="preserve">2026-09-18 11:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:36</t>
+    <t xml:space="preserve">2026-09-23 15:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:42</t>
+    <t xml:space="preserve">2026-10-04 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2022_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:49</t>
+    <t xml:space="preserve">2026-10-05 16:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
